--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -420,57 +420,55 @@
     <t>初級指南書</t>
   </si>
   <si>
-    <t>Expを50入手する
-Lvが10以下の場合は取得経験値が2倍になる</t>
+    <t>Exp+25
+Lvが10以下の場合はExp+100</t>
   </si>
   <si>
     <t>Beginner Guidebook</t>
   </si>
   <si>
+    <t>Gain 25 Exp
+If Lv is 10 or below, Gain 100 Exp</t>
+  </si>
+  <si>
+    <t>中級指南書</t>
+  </si>
+  <si>
+    <t>Exp+50
+Lvが20以下の場合はExp+100</t>
+  </si>
+  <si>
+    <t>Intermediate Guidebook</t>
+  </si>
+  <si>
     <t>Gain 50 Exp
-If Lv is 10 or below, received EXP is doubled</t>
-  </si>
-  <si>
-    <t>中級指南書</t>
-  </si>
-  <si>
-    <t>Expを50入手する
-Lvが20以下の場合は取得経験値が2倍になる</t>
-  </si>
-  <si>
-    <t>Intermediate Guidebook</t>
-  </si>
-  <si>
-    <t>Gain 50 Exp
-If Lv is 20 or below, received EXP is doubled</t>
+If Lv is 20 or below, Gain 100 Exp</t>
   </si>
   <si>
     <t>上級指南書</t>
   </si>
   <si>
-    <t>Expを50入手する
-Lvが30以下の場合は取得経験値が2倍になる</t>
+    <t>Exp+75
+Lvが30以下の場合はExp+100</t>
   </si>
   <si>
     <t>Advanced Guidebook</t>
   </si>
   <si>
-    <t>Gain 50 Exp
-If Lv is 30 or below, received EXP is doubled</t>
+    <t>Gain 75 Exp
+If Lv is 30 or below, Gain 100 Exp</t>
   </si>
   <si>
     <t>特級指南書</t>
   </si>
   <si>
-    <t>Expを50入手する
-Lvが40以下の場合は取得経験値が2倍になる</t>
+    <t>Exp+100</t>
   </si>
   <si>
     <t>Expert Guidebook</t>
   </si>
   <si>
-    <t>Gain 50 Exp
-If Lv is 40 or below, received EXP is doubled</t>
+    <t>Gain 100 Exp</t>
   </si>
   <si>
     <t>レッドスピネル</t>
@@ -723,9 +721,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -744,14 +742,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -772,16 +770,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -795,18 +793,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -834,7 +832,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -843,29 +841,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -880,8 +855,31 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -902,31 +900,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -950,7 +930,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -968,7 +978,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -980,7 +996,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -992,25 +1056,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1022,67 +1068,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1144,15 +1142,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -1165,6 +1154,24 @@
         <color theme="4"/>
       </top>
       <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1184,15 +1191,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1201,145 +1199,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2566,13 +2564,13 @@
         <v>10</v>
       </c>
       <c r="E39">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F39">
         <v>10</v>
       </c>
       <c r="G39" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2595,7 +2593,7 @@
         <v>20</v>
       </c>
       <c r="G40" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2618,7 +2616,7 @@
         <v>30</v>
       </c>
       <c r="G41" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2641,7 +2639,7 @@
         <v>40</v>
       </c>
       <c r="G42" s="1">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2664,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2687,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2710,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2733,7 +2731,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2756,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3699,7 +3697,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="39" ht="39" spans="1:7">
+    <row r="39" ht="26" spans="1:7">
       <c r="A39">
         <v>4010</v>
       </c>
@@ -3716,7 +3714,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="40" ht="39" spans="1:7">
+    <row r="40" ht="26" spans="1:7">
       <c r="A40">
         <v>4020</v>
       </c>
@@ -3733,7 +3731,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="41" ht="39" spans="1:7">
+    <row r="41" ht="26" spans="1:7">
       <c r="A41">
         <v>4030</v>
       </c>
@@ -3750,7 +3748,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="42" ht="39" spans="1:7">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>4040</v>
       </c>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="229">
   <si>
     <t>Id</t>
   </si>
@@ -385,6 +385,12 @@
   </si>
   <si>
     <t>Seven`s Stone</t>
+  </si>
+  <si>
+    <t>ファーストトリック</t>
+  </si>
+  <si>
+    <t>First Trick</t>
   </si>
   <si>
     <t>ヒールユニット</t>
@@ -721,9 +727,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -742,14 +748,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -757,7 +771,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -771,53 +792,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -833,6 +808,37 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -840,15 +846,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -864,14 +862,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -879,7 +877,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -900,19 +906,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -930,7 +948,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -942,49 +1032,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1002,85 +1074,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1109,17 +1115,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1135,15 +1150,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1177,16 +1183,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1199,145 +1205,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1673,7 +1679,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1719,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1742,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1765,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1788,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1811,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1834,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1857,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1880,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1903,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1926,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1949,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1972,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>20</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2483,7 +2489,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>2130</v>
+        <v>2110</v>
       </c>
       <c r="B36">
         <v>58</v>
@@ -2492,7 +2498,7 @@
         <v>20</v>
       </c>
       <c r="D36">
-        <v>310130</v>
+        <v>310110</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2506,16 +2512,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>3010</v>
+        <v>2130</v>
       </c>
       <c r="B37">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="C37">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D37">
-        <v>50</v>
+        <v>310130</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2529,7 +2535,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B38">
         <v>231</v>
@@ -2538,7 +2544,7 @@
         <v>30</v>
       </c>
       <c r="D38">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2552,30 +2558,30 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B39">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C39">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E39">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>10</v>
-      </c>
-      <c r="G39" s="1">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B40">
         <v>220</v>
@@ -2587,18 +2593,18 @@
         <v>10</v>
       </c>
       <c r="E40">
+        <v>25</v>
+      </c>
+      <c r="F40">
+        <v>10</v>
+      </c>
+      <c r="G40" s="1">
         <v>50</v>
-      </c>
-      <c r="F40">
-        <v>20</v>
-      </c>
-      <c r="G40" s="1">
-        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="B41">
         <v>220</v>
@@ -2613,15 +2619,15 @@
         <v>50</v>
       </c>
       <c r="F41">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G41" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="B42">
         <v>220</v>
@@ -2633,41 +2639,41 @@
         <v>10</v>
       </c>
       <c r="E42">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F42">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G42" s="1">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>4110</v>
+        <v>4040</v>
       </c>
       <c r="B43">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C43">
         <v>40</v>
       </c>
       <c r="D43">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G43" s="1">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B44">
         <v>224</v>
@@ -2679,7 +2685,7 @@
         <v>20</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -2690,7 +2696,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B45">
         <v>224</v>
@@ -2702,7 +2708,7 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -2713,7 +2719,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B46">
         <v>224</v>
@@ -2725,7 +2731,7 @@
         <v>20</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2736,7 +2742,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B47">
         <v>224</v>
@@ -2748,7 +2754,7 @@
         <v>20</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -2759,33 +2765,33 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B48">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C48">
         <v>40</v>
       </c>
       <c r="D48">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B49">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C49">
         <v>40</v>
@@ -2794,7 +2800,7 @@
         <v>30</v>
       </c>
       <c r="E49">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -2805,10 +2811,10 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B50">
-        <v>117</v>
+        <v>202</v>
       </c>
       <c r="C50">
         <v>40</v>
@@ -2817,7 +2823,7 @@
         <v>30</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -2828,10 +2834,10 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B51">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C51">
         <v>40</v>
@@ -2840,7 +2846,7 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -2851,10 +2857,10 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>4250</v>
+        <v>4240</v>
       </c>
       <c r="B52">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="C52">
         <v>40</v>
@@ -2863,7 +2869,7 @@
         <v>30</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -2874,53 +2880,53 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>4310</v>
+        <v>4250</v>
       </c>
       <c r="B53">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="C53">
         <v>40</v>
       </c>
       <c r="D53">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="B54">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C54">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D54">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E54">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>20</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B55">
         <v>125</v>
@@ -2932,7 +2938,7 @@
         <v>50</v>
       </c>
       <c r="E55">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F55">
         <v>25</v>
@@ -2943,7 +2949,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B56">
         <v>125</v>
@@ -2955,7 +2961,7 @@
         <v>50</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F56">
         <v>25</v>
@@ -2966,7 +2972,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="B57">
         <v>125</v>
@@ -2975,13 +2981,13 @@
         <v>50</v>
       </c>
       <c r="D57">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E57">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G57" s="1">
         <v>20</v>
@@ -2989,7 +2995,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="B58">
         <v>125</v>
@@ -2998,21 +3004,21 @@
         <v>50</v>
       </c>
       <c r="D58">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E58">
+        <v>10</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
         <v>20</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1">
-        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="B59">
         <v>125</v>
@@ -3024,12 +3030,35 @@
         <v>70</v>
       </c>
       <c r="E59">
+        <v>20</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
         <v>50</v>
       </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>5060</v>
+      </c>
+      <c r="B60">
+        <v>125</v>
+      </c>
+      <c r="C60">
+        <v>50</v>
+      </c>
+      <c r="D60">
+        <v>70</v>
+      </c>
+      <c r="E60">
+        <v>50</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
         <v>100</v>
       </c>
     </row>
@@ -3042,7 +3071,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
@@ -3648,7 +3677,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>2130</v>
+        <v>2110</v>
       </c>
       <c r="B36" t="s">
         <v>123</v>
@@ -3665,393 +3694,410 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>3010</v>
-      </c>
-      <c r="B37" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B37" t="s">
         <v>125</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
+        <v>102</v>
+      </c>
+      <c r="F37" t="s">
         <v>126</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>128</v>
+      <c r="G37" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
+        <v>3010</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
         <v>3020</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="39" ht="26" spans="1:7">
-      <c r="A39">
-        <v>4010</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="F39" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="G39" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="F39" t="s">
-        <v>135</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="40" ht="26" spans="1:7">
       <c r="A40">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B40" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F40" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="G40" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F40" t="s">
-        <v>139</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:7">
       <c r="A41">
+        <v>4020</v>
+      </c>
+      <c r="B41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" t="s">
+        <v>141</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" ht="26" spans="1:7">
+      <c r="A42">
         <v>4030</v>
       </c>
-      <c r="B41" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="B42" t="s">
         <v>143</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>4040</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="F42" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F42" t="s">
-        <v>147</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>4110</v>
+        <v>4040</v>
       </c>
       <c r="B43" t="s">
+        <v>147</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F43" t="s">
         <v>149</v>
       </c>
-      <c r="C43" t="s">
+      <c r="G43" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="F43" t="s">
-        <v>151</v>
-      </c>
-      <c r="G43" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B44" t="s">
+        <v>151</v>
+      </c>
+      <c r="C44" t="s">
+        <v>152</v>
+      </c>
+      <c r="F44" t="s">
         <v>153</v>
       </c>
-      <c r="C44" t="s">
+      <c r="G44" t="s">
         <v>154</v>
-      </c>
-      <c r="F44" t="s">
-        <v>155</v>
-      </c>
-      <c r="G44" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B45" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" t="s">
+        <v>156</v>
+      </c>
+      <c r="F45" t="s">
         <v>157</v>
       </c>
-      <c r="C45" t="s">
+      <c r="G45" t="s">
         <v>158</v>
-      </c>
-      <c r="F45" t="s">
-        <v>159</v>
-      </c>
-      <c r="G45" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" t="s">
+        <v>160</v>
+      </c>
+      <c r="F46" t="s">
         <v>161</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G46" t="s">
         <v>162</v>
-      </c>
-      <c r="F46" t="s">
-        <v>163</v>
-      </c>
-      <c r="G46" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B47" t="s">
+        <v>163</v>
+      </c>
+      <c r="C47" t="s">
+        <v>164</v>
+      </c>
+      <c r="F47" t="s">
         <v>165</v>
       </c>
-      <c r="C47" t="s">
+      <c r="G47" t="s">
         <v>166</v>
-      </c>
-      <c r="F47" t="s">
-        <v>167</v>
-      </c>
-      <c r="G47" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B48" t="s">
+        <v>167</v>
+      </c>
+      <c r="C48" t="s">
+        <v>168</v>
+      </c>
+      <c r="F48" t="s">
         <v>169</v>
       </c>
-      <c r="C48" t="s">
+      <c r="G48" t="s">
         <v>170</v>
-      </c>
-      <c r="F48" t="s">
-        <v>171</v>
-      </c>
-      <c r="G48" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" t="s">
+        <v>172</v>
+      </c>
+      <c r="F49" t="s">
         <v>173</v>
       </c>
-      <c r="C49" t="s">
+      <c r="G49" t="s">
         <v>174</v>
-      </c>
-      <c r="F49" t="s">
-        <v>175</v>
-      </c>
-      <c r="G49" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B50" t="s">
+        <v>175</v>
+      </c>
+      <c r="C50" t="s">
+        <v>176</v>
+      </c>
+      <c r="F50" t="s">
         <v>177</v>
       </c>
-      <c r="C50" t="s">
+      <c r="G50" t="s">
         <v>178</v>
-      </c>
-      <c r="F50" t="s">
-        <v>179</v>
-      </c>
-      <c r="G50" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B51" t="s">
+        <v>179</v>
+      </c>
+      <c r="C51" t="s">
+        <v>180</v>
+      </c>
+      <c r="F51" t="s">
         <v>181</v>
       </c>
-      <c r="C51" t="s">
+      <c r="G51" t="s">
         <v>182</v>
-      </c>
-      <c r="F51" t="s">
-        <v>183</v>
-      </c>
-      <c r="G51" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>4250</v>
+        <v>4240</v>
       </c>
       <c r="B52" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" t="s">
+        <v>184</v>
+      </c>
+      <c r="F52" t="s">
         <v>185</v>
       </c>
-      <c r="C52" t="s">
+      <c r="G52" t="s">
         <v>186</v>
-      </c>
-      <c r="F52" t="s">
-        <v>187</v>
-      </c>
-      <c r="G52" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
+        <v>4250</v>
+      </c>
+      <c r="B53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" t="s">
+        <v>189</v>
+      </c>
+      <c r="G53" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
         <v>4310</v>
       </c>
-      <c r="B53" t="s">
-        <v>189</v>
-      </c>
-      <c r="C53" t="s">
-        <v>190</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="B54" t="s">
         <v>191</v>
       </c>
-      <c r="G53" t="s">
+      <c r="C54" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="54" ht="39" spans="1:7">
-      <c r="A54">
-        <v>5010</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="F54" t="s">
         <v>193</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="G54" t="s">
         <v>194</v>
-      </c>
-      <c r="F54" t="s">
-        <v>195</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="55" ht="39" spans="1:7">
       <c r="A55">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B55" t="s">
+        <v>195</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F55" t="s">
         <v>197</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="G55" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="F55" t="s">
-        <v>199</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="56" ht="39" spans="1:7">
       <c r="A56">
+        <v>5020</v>
+      </c>
+      <c r="B56" t="s">
+        <v>199</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F56" t="s">
+        <v>201</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57" ht="39" spans="1:7">
+      <c r="A57">
         <v>5030</v>
       </c>
-      <c r="B56" t="s">
-        <v>201</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="B57" t="s">
         <v>203</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57">
+      <c r="F57" t="s">
+        <v>205</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
         <v>5040</v>
       </c>
-      <c r="B57" t="s">
-        <v>205</v>
-      </c>
-      <c r="C57" t="s">
-        <v>206</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="B58" t="s">
         <v>207</v>
       </c>
-      <c r="G57" t="s">
+      <c r="C58" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="58" ht="26" spans="1:7">
-      <c r="A58">
-        <v>5050</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="F58" t="s">
         <v>209</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="G58" t="s">
         <v>210</v>
-      </c>
-      <c r="F58" t="s">
-        <v>211</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="59" ht="26" spans="1:7">
       <c r="A59">
+        <v>5050</v>
+      </c>
+      <c r="B59" t="s">
+        <v>211</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F59" t="s">
+        <v>213</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60" ht="26" spans="1:7">
+      <c r="A60">
         <v>5060</v>
       </c>
-      <c r="B59" t="s">
-        <v>213</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="B60" t="s">
         <v>215</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>216</v>
+      </c>
+      <c r="F60" t="s">
+        <v>217</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -4071,7 +4117,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4079,10 +4125,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4090,10 +4136,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4101,10 +4147,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4112,7 +4158,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4120,7 +4166,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4128,7 +4174,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="233">
   <si>
     <t>Id</t>
   </si>
@@ -411,16 +411,28 @@
     <t>Can be exchanged for 50 Nu</t>
   </si>
   <si>
+    <t>黒真珠</t>
+  </si>
+  <si>
+    <t>150(Nu)に換金できる</t>
+  </si>
+  <si>
+    <t>Black Pearl</t>
+  </si>
+  <si>
+    <t>Can be exchanged for 150 Nu</t>
+  </si>
+  <si>
     <t>ダイアモンド</t>
   </si>
   <si>
-    <t>200(Nu)に換金できる</t>
+    <t>300(Nu)に換金できる</t>
   </si>
   <si>
     <t>Diamond</t>
   </si>
   <si>
-    <t>Can be exchanged for 200 Nu</t>
+    <t>Can be exchanged for 300 Nu</t>
   </si>
   <si>
     <t>初級指南書</t>
@@ -726,10 +738,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -751,6 +763,83 @@
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -777,97 +866,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -883,9 +881,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -906,7 +918,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -918,13 +1050,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -936,103 +1074,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1044,49 +1092,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1100,41 +1112,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1154,13 +1138,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1183,6 +1171,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1197,6 +1200,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1205,7 +1217,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1214,136 +1226,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1679,7 +1691,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2567,7 +2579,7 @@
         <v>30</v>
       </c>
       <c r="D39">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2581,30 +2593,30 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="B40">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C40">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="E40">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>10</v>
-      </c>
-      <c r="G40" s="1">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B41">
         <v>220</v>
@@ -2616,18 +2628,18 @@
         <v>10</v>
       </c>
       <c r="E41">
+        <v>25</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="G41" s="1">
         <v>50</v>
-      </c>
-      <c r="F41">
-        <v>20</v>
-      </c>
-      <c r="G41" s="1">
-        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="B42">
         <v>220</v>
@@ -2639,18 +2651,18 @@
         <v>10</v>
       </c>
       <c r="E42">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F42">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G42" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="B43">
         <v>220</v>
@@ -2662,41 +2674,41 @@
         <v>10</v>
       </c>
       <c r="E43">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F43">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G43" s="1">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>4110</v>
+        <v>4040</v>
       </c>
       <c r="B44">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C44">
         <v>40</v>
       </c>
       <c r="D44">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G44" s="1">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B45">
         <v>224</v>
@@ -2708,7 +2720,7 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -2719,7 +2731,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B46">
         <v>224</v>
@@ -2731,7 +2743,7 @@
         <v>20</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2742,7 +2754,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B47">
         <v>224</v>
@@ -2754,7 +2766,7 @@
         <v>20</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -2765,7 +2777,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B48">
         <v>224</v>
@@ -2777,7 +2789,7 @@
         <v>20</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -2788,33 +2800,33 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B49">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C49">
         <v>40</v>
       </c>
       <c r="D49">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B50">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C50">
         <v>40</v>
@@ -2823,7 +2835,7 @@
         <v>30</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -2834,10 +2846,10 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B51">
-        <v>117</v>
+        <v>202</v>
       </c>
       <c r="C51">
         <v>40</v>
@@ -2846,7 +2858,7 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -2857,10 +2869,10 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B52">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C52">
         <v>40</v>
@@ -2869,7 +2881,7 @@
         <v>30</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -2880,10 +2892,10 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>4250</v>
+        <v>4240</v>
       </c>
       <c r="B53">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="C53">
         <v>40</v>
@@ -2892,7 +2904,7 @@
         <v>30</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -2903,53 +2915,53 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>4310</v>
+        <v>4250</v>
       </c>
       <c r="B54">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="C54">
         <v>40</v>
       </c>
       <c r="D54">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" s="1">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="B55">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C55">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D55">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E55">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G55" s="1">
-        <v>20</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B56">
         <v>125</v>
@@ -2961,7 +2973,7 @@
         <v>50</v>
       </c>
       <c r="E56">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F56">
         <v>25</v>
@@ -2972,7 +2984,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B57">
         <v>125</v>
@@ -2984,7 +2996,7 @@
         <v>50</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F57">
         <v>25</v>
@@ -2995,7 +3007,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="B58">
         <v>125</v>
@@ -3004,13 +3016,13 @@
         <v>50</v>
       </c>
       <c r="D58">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E58">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G58" s="1">
         <v>20</v>
@@ -3018,7 +3030,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="B59">
         <v>125</v>
@@ -3027,21 +3039,21 @@
         <v>50</v>
       </c>
       <c r="D59">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E59">
+        <v>10</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
         <v>20</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1">
-        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="B60">
         <v>125</v>
@@ -3053,12 +3065,35 @@
         <v>70</v>
       </c>
       <c r="E60">
+        <v>20</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
         <v>50</v>
       </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>5060</v>
+      </c>
+      <c r="B61">
+        <v>125</v>
+      </c>
+      <c r="C61">
+        <v>50</v>
+      </c>
+      <c r="D61">
+        <v>70</v>
+      </c>
+      <c r="E61">
+        <v>50</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
         <v>100</v>
       </c>
     </row>
@@ -3071,7 +3106,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
@@ -3743,26 +3778,26 @@
         <v>134</v>
       </c>
     </row>
-    <row r="40" ht="26" spans="1:7">
+    <row r="40" spans="1:7">
       <c r="A40">
-        <v>4010</v>
-      </c>
-      <c r="B40" t="s">
+        <v>3030</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="1" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="41" ht="26" spans="1:7">
       <c r="A41">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B41" t="s">
         <v>139</v>
@@ -3779,7 +3814,7 @@
     </row>
     <row r="42" ht="26" spans="1:7">
       <c r="A42">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="B42" t="s">
         <v>143</v>
@@ -3794,9 +3829,9 @@
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" ht="26" spans="1:7">
       <c r="A43">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="B43" t="s">
         <v>147</v>
@@ -3813,24 +3848,24 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>4110</v>
+        <v>4040</v>
       </c>
       <c r="B44" t="s">
         <v>151</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F44" t="s">
         <v>153</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B45" t="s">
         <v>155</v>
@@ -3847,7 +3882,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B46" t="s">
         <v>159</v>
@@ -3864,7 +3899,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B47" t="s">
         <v>163</v>
@@ -3881,7 +3916,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B48" t="s">
         <v>167</v>
@@ -3898,7 +3933,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B49" t="s">
         <v>171</v>
@@ -3915,7 +3950,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B50" t="s">
         <v>175</v>
@@ -3932,7 +3967,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B51" t="s">
         <v>179</v>
@@ -3949,7 +3984,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B52" t="s">
         <v>183</v>
@@ -3966,7 +4001,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>4250</v>
+        <v>4240</v>
       </c>
       <c r="B53" t="s">
         <v>187</v>
@@ -3983,7 +4018,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>4310</v>
+        <v>4250</v>
       </c>
       <c r="B54" t="s">
         <v>191</v>
@@ -3998,26 +4033,26 @@
         <v>194</v>
       </c>
     </row>
-    <row r="55" ht="39" spans="1:7">
+    <row r="55" spans="1:7">
       <c r="A55">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="B55" t="s">
         <v>195</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" t="s">
         <v>196</v>
       </c>
       <c r="F55" t="s">
         <v>197</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="56" ht="39" spans="1:7">
       <c r="A56">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B56" t="s">
         <v>199</v>
@@ -4034,7 +4069,7 @@
     </row>
     <row r="57" ht="39" spans="1:7">
       <c r="A57">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B57" t="s">
         <v>203</v>
@@ -4049,43 +4084,43 @@
         <v>206</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" ht="39" spans="1:7">
       <c r="A58">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="B58" t="s">
         <v>207</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="2" t="s">
         <v>208</v>
       </c>
       <c r="F58" t="s">
         <v>209</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="59" ht="26" spans="1:7">
+    <row r="59" spans="1:7">
       <c r="A59">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="B59" t="s">
         <v>211</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" t="s">
         <v>212</v>
       </c>
       <c r="F59" t="s">
         <v>213</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="G59" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="60" ht="26" spans="1:7">
       <c r="A60">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="B60" t="s">
         <v>215</v>
@@ -4098,6 +4133,23 @@
       </c>
       <c r="G60" s="2" t="s">
         <v>218</v>
+      </c>
+    </row>
+    <row r="61" ht="26" spans="1:7">
+      <c r="A61">
+        <v>5060</v>
+      </c>
+      <c r="B61" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F61" t="s">
+        <v>221</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -4117,7 +4169,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4125,10 +4177,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4136,10 +4188,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4147,10 +4199,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4158,7 +4210,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4166,7 +4218,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4174,7 +4226,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -612,7 +612,8 @@
     <t>マスタープルフ</t>
   </si>
   <si>
-    <t>クラスチェンジできる</t>
+    <t>クラスチェンジする
+装備可能枠が1つ増え各スタータスも強化する</t>
   </si>
   <si>
     <t>Master Puff</t>
@@ -738,10 +739,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -766,6 +767,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -775,7 +798,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -795,11 +841,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -808,6 +861,14 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -820,31 +881,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -858,46 +896,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -918,7 +919,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -930,7 +961,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -942,19 +985,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -966,7 +1003,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -978,55 +1021,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1038,49 +1033,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1098,7 +1057,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1114,11 +1115,48 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1138,17 +1176,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1158,15 +1192,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1185,30 +1210,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1217,7 +1218,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1226,145 +1227,148 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2132,22 +2136,22 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="3">
+      <c r="A20" s="4">
         <v>1300</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>11</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="4">
         <v>11</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="4">
         <v>110</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="4">
         <v>-1</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <v>0</v>
       </c>
       <c r="G20">
@@ -2155,22 +2159,22 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="3">
+      <c r="A21" s="4">
         <v>1310</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>11</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>11</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>110</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="4">
         <v>0</v>
       </c>
       <c r="G21">
@@ -2178,22 +2182,22 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="3">
+      <c r="A22" s="4">
         <v>1320</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>11</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="4">
         <v>11</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="4">
         <v>110</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="4">
         <v>2</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="4">
         <v>0</v>
       </c>
       <c r="G22">
@@ -2201,22 +2205,22 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="3">
+      <c r="A23" s="4">
         <v>1330</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>11</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="4">
         <v>11</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="4">
         <v>110</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="4">
         <v>3</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="4">
         <v>0</v>
       </c>
       <c r="G23">
@@ -2224,22 +2228,22 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="3">
+      <c r="A24" s="4">
         <v>1340</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>11</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="4">
         <v>11</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="4">
         <v>110</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="4">
         <v>4</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="4">
         <v>0</v>
       </c>
       <c r="G24">
@@ -2247,22 +2251,22 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>1350</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>11</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="4">
         <v>11</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="4">
         <v>110</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="4">
         <v>5</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="4">
         <v>0</v>
       </c>
       <c r="G25">
@@ -4033,14 +4037,14 @@
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" ht="39" spans="1:7">
       <c r="A55">
         <v>4310</v>
       </c>
       <c r="B55" t="s">
         <v>195</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="3" t="s">
         <v>196</v>
       </c>
       <c r="F55" t="s">

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="235">
   <si>
     <t>Id</t>
   </si>
@@ -391,6 +391,12 @@
   </si>
   <si>
     <t>First Trick</t>
+  </si>
+  <si>
+    <t>リカバリーエンハンス</t>
+  </si>
+  <si>
+    <t>Recovery Enhance</t>
   </si>
   <si>
     <t>ヒールユニット</t>
@@ -740,9 +746,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -760,8 +766,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -775,45 +820,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -828,27 +836,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -856,9 +849,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -872,33 +888,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -919,7 +925,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -931,7 +1003,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -943,7 +1069,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -955,151 +1099,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1113,20 +1119,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1142,21 +1145,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1178,6 +1166,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1191,22 +1203,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1218,157 +1224,154 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1695,7 +1698,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2136,22 +2139,22 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>1300</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="3">
         <v>11</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="3">
         <v>11</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>110</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>-1</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20">
@@ -2159,22 +2162,22 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>1310</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="3">
         <v>11</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>11</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>110</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>1</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="3">
         <v>0</v>
       </c>
       <c r="G21">
@@ -2182,22 +2185,22 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>1320</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>11</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="3">
         <v>11</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>110</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>2</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <v>0</v>
       </c>
       <c r="G22">
@@ -2205,22 +2208,22 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>1330</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="3">
         <v>11</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="3">
         <v>11</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>110</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="3">
         <v>3</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23">
@@ -2228,22 +2231,22 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>1340</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="3">
         <v>11</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <v>11</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>110</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="3">
         <v>4</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24">
@@ -2251,22 +2254,22 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>1350</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="3">
         <v>11</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>11</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>110</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="3">
         <v>5</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="3">
         <v>0</v>
       </c>
       <c r="G25">
@@ -2528,7 +2531,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B37">
         <v>58</v>
@@ -2537,7 +2540,7 @@
         <v>20</v>
       </c>
       <c r="D37">
-        <v>310130</v>
+        <v>310120</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2551,16 +2554,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>3010</v>
+        <v>2130</v>
       </c>
       <c r="B38">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="C38">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D38">
-        <v>50</v>
+        <v>310130</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2574,7 +2577,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B39">
         <v>231</v>
@@ -2583,7 +2586,7 @@
         <v>30</v>
       </c>
       <c r="D39">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2597,7 +2600,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B40">
         <v>231</v>
@@ -2606,7 +2609,7 @@
         <v>30</v>
       </c>
       <c r="D40">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2620,30 +2623,30 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="B41">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C41">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="E41">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>10</v>
-      </c>
-      <c r="G41" s="1">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B42">
         <v>220</v>
@@ -2655,18 +2658,18 @@
         <v>10</v>
       </c>
       <c r="E42">
+        <v>25</v>
+      </c>
+      <c r="F42">
+        <v>10</v>
+      </c>
+      <c r="G42" s="1">
         <v>50</v>
-      </c>
-      <c r="F42">
-        <v>20</v>
-      </c>
-      <c r="G42" s="1">
-        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>4030</v>
+        <v>4020</v>
       </c>
       <c r="B43">
         <v>220</v>
@@ -2678,18 +2681,18 @@
         <v>10</v>
       </c>
       <c r="E43">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F43">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G43" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>4040</v>
+        <v>4030</v>
       </c>
       <c r="B44">
         <v>220</v>
@@ -2701,41 +2704,41 @@
         <v>10</v>
       </c>
       <c r="E44">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F44">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G44" s="1">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4110</v>
+        <v>4040</v>
       </c>
       <c r="B45">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C45">
         <v>40</v>
       </c>
       <c r="D45">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G45" s="1">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B46">
         <v>224</v>
@@ -2747,7 +2750,7 @@
         <v>20</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2758,7 +2761,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B47">
         <v>224</v>
@@ -2770,7 +2773,7 @@
         <v>20</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -2781,7 +2784,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B48">
         <v>224</v>
@@ -2793,7 +2796,7 @@
         <v>20</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -2804,7 +2807,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B49">
         <v>224</v>
@@ -2816,7 +2819,7 @@
         <v>20</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -2827,33 +2830,33 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B50">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C50">
         <v>40</v>
       </c>
       <c r="D50">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B51">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C51">
         <v>40</v>
@@ -2862,7 +2865,7 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -2873,10 +2876,10 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B52">
-        <v>117</v>
+        <v>202</v>
       </c>
       <c r="C52">
         <v>40</v>
@@ -2885,7 +2888,7 @@
         <v>30</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -2896,10 +2899,10 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B53">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C53">
         <v>40</v>
@@ -2908,7 +2911,7 @@
         <v>30</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -2919,10 +2922,10 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>4250</v>
+        <v>4240</v>
       </c>
       <c r="B54">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="C54">
         <v>40</v>
@@ -2931,7 +2934,7 @@
         <v>30</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -2942,53 +2945,53 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>4310</v>
+        <v>4250</v>
       </c>
       <c r="B55">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="C55">
         <v>40</v>
       </c>
       <c r="D55">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" s="1">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="B56">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C56">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D56">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E56">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>20</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B57">
         <v>125</v>
@@ -3000,7 +3003,7 @@
         <v>50</v>
       </c>
       <c r="E57">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F57">
         <v>25</v>
@@ -3011,7 +3014,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="B58">
         <v>125</v>
@@ -3023,7 +3026,7 @@
         <v>50</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F58">
         <v>25</v>
@@ -3034,7 +3037,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="B59">
         <v>125</v>
@@ -3043,13 +3046,13 @@
         <v>50</v>
       </c>
       <c r="D59">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E59">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G59" s="1">
         <v>20</v>
@@ -3057,7 +3060,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="B60">
         <v>125</v>
@@ -3066,21 +3069,21 @@
         <v>50</v>
       </c>
       <c r="D60">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E60">
+        <v>10</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
         <v>20</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1">
-        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>5060</v>
+        <v>5050</v>
       </c>
       <c r="B61">
         <v>125</v>
@@ -3092,12 +3095,35 @@
         <v>70</v>
       </c>
       <c r="E61">
+        <v>20</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
         <v>50</v>
       </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1">
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>5060</v>
+      </c>
+      <c r="B62">
+        <v>125</v>
+      </c>
+      <c r="C62">
+        <v>50</v>
+      </c>
+      <c r="D62">
+        <v>70</v>
+      </c>
+      <c r="E62">
+        <v>50</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
         <v>100</v>
       </c>
     </row>
@@ -3110,7 +3136,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="19.8181818181818" customWidth="1"/>
@@ -3733,7 +3759,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B37" t="s">
         <v>125</v>
@@ -3750,410 +3776,427 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>3010</v>
-      </c>
-      <c r="B38" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B38" t="s">
         <v>127</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
+        <v>102</v>
+      </c>
+      <c r="F38" t="s">
         <v>128</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>130</v>
+      <c r="G38" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
+        <v>3020</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
         <v>3030</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="41" ht="26" spans="1:7">
-      <c r="A41">
-        <v>4010</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="F41" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="G41" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="F41" t="s">
-        <v>141</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="42" ht="26" spans="1:7">
       <c r="A42">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B42" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F42" t="s">
         <v>143</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="F42" t="s">
-        <v>145</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="43" ht="26" spans="1:7">
       <c r="A43">
+        <v>4020</v>
+      </c>
+      <c r="B43" t="s">
+        <v>145</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F43" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" ht="26" spans="1:7">
+      <c r="A44">
         <v>4030</v>
       </c>
-      <c r="B43" t="s">
-        <v>147</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="B44" t="s">
         <v>149</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>4040</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="F44" t="s">
         <v>151</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F44" t="s">
-        <v>153</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>4110</v>
+        <v>4040</v>
       </c>
       <c r="B45" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" t="s">
         <v>155</v>
       </c>
-      <c r="C45" t="s">
+      <c r="G45" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="F45" t="s">
-        <v>157</v>
-      </c>
-      <c r="G45" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>4120</v>
+        <v>4110</v>
       </c>
       <c r="B46" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" t="s">
+        <v>158</v>
+      </c>
+      <c r="F46" t="s">
         <v>159</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G46" t="s">
         <v>160</v>
-      </c>
-      <c r="F46" t="s">
-        <v>161</v>
-      </c>
-      <c r="G46" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>4130</v>
+        <v>4120</v>
       </c>
       <c r="B47" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" t="s">
+        <v>162</v>
+      </c>
+      <c r="F47" t="s">
         <v>163</v>
       </c>
-      <c r="C47" t="s">
+      <c r="G47" t="s">
         <v>164</v>
-      </c>
-      <c r="F47" t="s">
-        <v>165</v>
-      </c>
-      <c r="G47" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>4140</v>
+        <v>4130</v>
       </c>
       <c r="B48" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" t="s">
+        <v>166</v>
+      </c>
+      <c r="F48" t="s">
         <v>167</v>
       </c>
-      <c r="C48" t="s">
+      <c r="G48" t="s">
         <v>168</v>
-      </c>
-      <c r="F48" t="s">
-        <v>169</v>
-      </c>
-      <c r="G48" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>4150</v>
+        <v>4140</v>
       </c>
       <c r="B49" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" t="s">
+        <v>170</v>
+      </c>
+      <c r="F49" t="s">
         <v>171</v>
       </c>
-      <c r="C49" t="s">
+      <c r="G49" t="s">
         <v>172</v>
-      </c>
-      <c r="F49" t="s">
-        <v>173</v>
-      </c>
-      <c r="G49" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>4210</v>
+        <v>4150</v>
       </c>
       <c r="B50" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" t="s">
+        <v>174</v>
+      </c>
+      <c r="F50" t="s">
         <v>175</v>
       </c>
-      <c r="C50" t="s">
+      <c r="G50" t="s">
         <v>176</v>
-      </c>
-      <c r="F50" t="s">
-        <v>177</v>
-      </c>
-      <c r="G50" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="B51" t="s">
+        <v>177</v>
+      </c>
+      <c r="C51" t="s">
+        <v>178</v>
+      </c>
+      <c r="F51" t="s">
         <v>179</v>
       </c>
-      <c r="C51" t="s">
+      <c r="G51" t="s">
         <v>180</v>
-      </c>
-      <c r="F51" t="s">
-        <v>181</v>
-      </c>
-      <c r="G51" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>4230</v>
+        <v>4220</v>
       </c>
       <c r="B52" t="s">
+        <v>181</v>
+      </c>
+      <c r="C52" t="s">
+        <v>182</v>
+      </c>
+      <c r="F52" t="s">
         <v>183</v>
       </c>
-      <c r="C52" t="s">
+      <c r="G52" t="s">
         <v>184</v>
-      </c>
-      <c r="F52" t="s">
-        <v>185</v>
-      </c>
-      <c r="G52" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>4240</v>
+        <v>4230</v>
       </c>
       <c r="B53" t="s">
+        <v>185</v>
+      </c>
+      <c r="C53" t="s">
+        <v>186</v>
+      </c>
+      <c r="F53" t="s">
         <v>187</v>
       </c>
-      <c r="C53" t="s">
+      <c r="G53" t="s">
         <v>188</v>
-      </c>
-      <c r="F53" t="s">
-        <v>189</v>
-      </c>
-      <c r="G53" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
+        <v>4240</v>
+      </c>
+      <c r="B54" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" t="s">
+        <v>190</v>
+      </c>
+      <c r="F54" t="s">
+        <v>191</v>
+      </c>
+      <c r="G54" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
         <v>4250</v>
       </c>
-      <c r="B54" t="s">
-        <v>191</v>
-      </c>
-      <c r="C54" t="s">
-        <v>192</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="B55" t="s">
         <v>193</v>
       </c>
-      <c r="G54" t="s">
+      <c r="C55" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="55" ht="39" spans="1:7">
-      <c r="A55">
-        <v>4310</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="F55" t="s">
         <v>195</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="G55" t="s">
         <v>196</v>
-      </c>
-      <c r="F55" t="s">
-        <v>197</v>
-      </c>
-      <c r="G55" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="56" ht="39" spans="1:7">
       <c r="A56">
-        <v>5010</v>
+        <v>4310</v>
       </c>
       <c r="B56" t="s">
+        <v>197</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F56" t="s">
         <v>199</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="G56" t="s">
         <v>200</v>
-      </c>
-      <c r="F56" t="s">
-        <v>201</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="57" ht="39" spans="1:7">
       <c r="A57">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="B57" t="s">
+        <v>201</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F57" t="s">
         <v>203</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="G57" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="F57" t="s">
-        <v>205</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="58" ht="39" spans="1:7">
       <c r="A58">
+        <v>5020</v>
+      </c>
+      <c r="B58" t="s">
+        <v>205</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F58" t="s">
+        <v>207</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="59" ht="39" spans="1:7">
+      <c r="A59">
         <v>5030</v>
       </c>
-      <c r="B58" t="s">
-        <v>207</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="B59" t="s">
         <v>209</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59">
+      <c r="F59" t="s">
+        <v>211</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
         <v>5040</v>
       </c>
-      <c r="B59" t="s">
-        <v>211</v>
-      </c>
-      <c r="C59" t="s">
-        <v>212</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="B60" t="s">
         <v>213</v>
       </c>
-      <c r="G59" t="s">
+      <c r="C60" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="60" ht="26" spans="1:7">
-      <c r="A60">
-        <v>5050</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="F60" t="s">
         <v>215</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="G60" t="s">
         <v>216</v>
-      </c>
-      <c r="F60" t="s">
-        <v>217</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="61" ht="26" spans="1:7">
       <c r="A61">
+        <v>5050</v>
+      </c>
+      <c r="B61" t="s">
+        <v>217</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F61" t="s">
+        <v>219</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62" ht="26" spans="1:7">
+      <c r="A62">
         <v>5060</v>
       </c>
-      <c r="B61" t="s">
-        <v>219</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="B62" t="s">
         <v>221</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>222</v>
+      </c>
+      <c r="F62" t="s">
+        <v>223</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -4173,7 +4216,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4181,10 +4224,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4192,10 +4235,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4203,10 +4246,10 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4214,7 +4257,7 @@
         <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4222,7 +4265,7 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4230,7 +4273,7 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Items.xlsx
+++ b/Assets/Data/Items.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Items" sheetId="1" r:id="rId1"/>
@@ -746,9 +746,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -766,6 +766,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -774,7 +812,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -782,6 +826,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -797,116 +902,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -925,19 +925,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -949,49 +1009,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1003,13 +1021,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1027,13 +1051,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1045,7 +1081,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1057,55 +1105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1116,6 +1116,41 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1134,17 +1169,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1160,15 +1189,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1190,26 +1210,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -1224,145 +1224,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>30</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>30</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>30</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>30</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2112,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>30</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>30</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:7">
